--- a/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>28605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>50461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>51353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77088</t>
+          <t>75911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85228</t>
+          <t>85148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118631</t>
+          <t>119041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140887</t>
+          <t>141366</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163983</t>
+          <t>163222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112685</t>
+          <t>113862</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138173</t>
+          <t>138420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262969</t>
+          <t>262559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>296372</t>
+          <t>296452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161300</t>
+          <t>161204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196172</t>
+          <t>195826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>294280</t>
+          <t>295235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328411</t>
+          <t>328963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>467757</t>
+          <t>465538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>514455</t>
+          <t>517280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111291</t>
+          <t>111637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146163</t>
+          <t>146259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79321</t>
+          <t>78769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113452</t>
+          <t>112497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>200740</t>
+          <t>197915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>247438</t>
+          <t>249657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286406</t>
+          <t>284426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>328377</t>
+          <t>331836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>386077</t>
+          <t>385074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>429970</t>
+          <t>431566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>684569</t>
+          <t>680254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>750545</t>
+          <t>744192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181952</t>
+          <t>178493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>223923</t>
+          <t>225903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159522</t>
+          <t>157926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>203415</t>
+          <t>204418</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349277</t>
+          <t>355630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>415253</t>
+          <t>419568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103506</t>
+          <t>100729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137464</t>
+          <t>135830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112353</t>
+          <t>112647</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144469</t>
+          <t>143742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223408</t>
+          <t>220787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271083</t>
+          <t>270292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152574</t>
+          <t>154208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186532</t>
+          <t>189309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93574</t>
+          <t>94301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125690</t>
+          <t>125396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256999</t>
+          <t>257790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>304674</t>
+          <t>307295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56229</t>
+          <t>57515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83430</t>
+          <t>83800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77546</t>
+          <t>77213</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108931</t>
+          <t>108502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76721</t>
+          <t>77331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93709</t>
+          <t>93573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116949</t>
+          <t>116579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144150</t>
+          <t>142864</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>199550</t>
+          <t>199979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230935</t>
+          <t>231268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>27123</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36729</t>
+          <t>36599</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61316</t>
+          <t>61536</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52311</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81886</t>
+          <t>80820</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266430</t>
+          <t>265460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281728</t>
+          <t>281352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280719</t>
+          <t>280499</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305306</t>
+          <t>305436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>552732</t>
+          <t>553798</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>582307</t>
+          <t>581823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>31210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>40793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>38215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>67028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177759</t>
+          <t>178673</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196006</t>
+          <t>195181</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>293741</t>
+          <t>293115</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314203</t>
+          <t>314639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478623</t>
+          <t>476763</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>506157</t>
+          <t>505576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>663183</t>
+          <t>666019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>748468</t>
+          <t>749273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1010970</t>
+          <t>1015276</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1103813</t>
+          <t>1109391</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1698885</t>
+          <t>1698777</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1829024</t>
+          <t>1830993</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1161758</t>
+          <t>1160953</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1247043</t>
+          <t>1244207</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1197549</t>
+          <t>1191971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1290392</t>
+          <t>1286086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2382564</t>
+          <t>2380595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2512703</t>
+          <t>2512811</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42851</t>
+          <t>41748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66628</t>
+          <t>68910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104137</t>
+          <t>104739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133851</t>
+          <t>132882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154728</t>
+          <t>152626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>194592</t>
+          <t>190474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109852</t>
+          <t>107570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133629</t>
+          <t>134732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82939</t>
+          <t>83908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112653</t>
+          <t>112051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198677</t>
+          <t>202795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238541</t>
+          <t>240643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>198561</t>
+          <t>200213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>235052</t>
+          <t>234041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>378541</t>
+          <t>378269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>401263</t>
+          <t>401701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>587100</t>
+          <t>588534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>630318</t>
+          <t>629190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85480</t>
+          <t>86491</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121971</t>
+          <t>120319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46255</t>
+          <t>46527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115010</t>
+          <t>116138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158228</t>
+          <t>156794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>401147</t>
+          <t>404524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>443159</t>
+          <t>445557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>565834</t>
+          <t>567435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>588687</t>
+          <t>588955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>975851</t>
+          <t>975867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1025009</t>
+          <t>1027941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126396</t>
+          <t>123998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168408</t>
+          <t>165031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21078</t>
+          <t>20810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>42330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154312</t>
+          <t>151380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203470</t>
+          <t>203454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220744</t>
+          <t>222162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261634</t>
+          <t>262739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252323</t>
+          <t>252400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276634</t>
+          <t>277849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>481039</t>
+          <t>483468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>530174</t>
+          <t>531302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,8%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113540</t>
+          <t>112435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154430</t>
+          <t>153012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55393</t>
+          <t>55316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152716</t>
+          <t>151588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201851</t>
+          <t>199422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52533</t>
+          <t>52673</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77486</t>
+          <t>76972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84114</t>
+          <t>84479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>115201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145615</t>
+          <t>146240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>184150</t>
+          <t>185228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64278</t>
+          <t>64792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89231</t>
+          <t>89091</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105320</t>
+          <t>106917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138004</t>
+          <t>137639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179732</t>
+          <t>178654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>218267</t>
+          <t>217642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43526</t>
+          <t>47123</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37787</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64435</t>
+          <t>64565</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65431</t>
+          <t>64705</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98122</t>
+          <t>100299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262461</t>
+          <t>258864</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284317</t>
+          <t>282768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>285475</t>
+          <t>285345</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312123</t>
+          <t>311688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>557775</t>
+          <t>555598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>590466</t>
+          <t>591192</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32893</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33485</t>
+          <t>33550</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58547</t>
+          <t>61029</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50352</t>
+          <t>51667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83772</t>
+          <t>83441</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>214942</t>
+          <t>215429</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235892</t>
+          <t>236065</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>327188</t>
+          <t>324706</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352250</t>
+          <t>352185</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>549798</t>
+          <t>550129</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>583218</t>
+          <t>581903</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1006826</t>
+          <t>1006836</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1101905</t>
+          <t>1105466</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1502778</t>
+          <t>1497883</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1597594</t>
+          <t>1594913</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2530825</t>
+          <t>2525671</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2673145</t>
+          <t>2665308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1035421</t>
+          <t>1031860</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1130500</t>
+          <t>1130490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>919236</t>
+          <t>921917</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1014052</t>
+          <t>1018947</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1981011</t>
+          <t>1988848</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2123331</t>
+          <t>2128485</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>37397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61930</t>
+          <t>62296</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88991</t>
+          <t>89734</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113665</t>
+          <t>114120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132853</t>
+          <t>132666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168875</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92799</t>
+          <t>92433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116360</t>
+          <t>117332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61284</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85958</t>
+          <t>85215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160803</t>
+          <t>159584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196825</t>
+          <t>197012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179561</t>
+          <t>178295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208872</t>
+          <t>208258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>297800</t>
+          <t>299095</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>322405</t>
+          <t>322802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>484974</t>
+          <t>484373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>525209</t>
+          <t>522791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51825</t>
+          <t>52439</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81136</t>
+          <t>82402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35988</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60593</t>
+          <t>59298</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93881</t>
+          <t>96299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134116</t>
+          <t>134717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>310706</t>
+          <t>314358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>352024</t>
+          <t>352789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>410725</t>
+          <t>413290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>448135</t>
+          <t>449489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>739039</t>
+          <t>737890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>791646</t>
+          <t>792094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112352</t>
+          <t>111587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153670</t>
+          <t>150018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93074</t>
+          <t>91720</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130484</t>
+          <t>127919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213938</t>
+          <t>213490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>266545</t>
+          <t>267694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153571</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192871</t>
+          <t>193381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174881</t>
+          <t>177841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211264</t>
+          <t>213682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342021</t>
+          <t>343139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394688</t>
+          <t>396733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,49%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147087</t>
+          <t>146577</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186387</t>
+          <t>185128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104592</t>
+          <t>102174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140975</t>
+          <t>138015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>261126</t>
+          <t>259081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313793</t>
+          <t>312675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32328</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54355</t>
+          <t>54229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48438</t>
+          <t>47447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>76060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86381</t>
+          <t>86702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120583</t>
+          <t>122389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75879</t>
+          <t>76005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97906</t>
+          <t>98052</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126370</t>
+          <t>128521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156143</t>
+          <t>157134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214232</t>
+          <t>212426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>248434</t>
+          <t>248113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35022</t>
+          <t>36338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59442</t>
+          <t>58882</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55196</t>
+          <t>54505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88485</t>
+          <t>87044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265606</t>
+          <t>264290</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284308</t>
+          <t>284795</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>286757</t>
+          <t>287317</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312665</t>
+          <t>312172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>558342</t>
+          <t>559783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>591631</t>
+          <t>592322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28139</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37095</t>
+          <t>38058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69701</t>
+          <t>67715</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54035</t>
+          <t>54011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89278</t>
+          <t>88944</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>218168</t>
+          <t>219388</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234231</t>
+          <t>234421</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>324132</t>
+          <t>326118</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356738</t>
+          <t>355775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>550862</t>
+          <t>551196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>586105</t>
+          <t>586129</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>794075</t>
+          <t>797796</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>880538</t>
+          <t>881605</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1142237</t>
+          <t>1146440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1246758</t>
+          <t>1247762</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1966355</t>
+          <t>1960395</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2099250</t>
+          <t>2097694</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1016390</t>
+          <t>1015323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1102853</t>
+          <t>1099132</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1088262</t>
+          <t>1087258</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1192783</t>
+          <t>1188580</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2132698</t>
+          <t>2134254</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2265593</t>
+          <t>2271553</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>33407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48556</t>
+          <t>50222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>375727</t>
+          <t>376050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395491</t>
+          <t>395979</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278112</t>
+          <t>279793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301176</t>
+          <t>302089</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>664631</t>
+          <t>662965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>692301</t>
+          <t>692242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52750</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106933</t>
+          <t>105444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86806</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145197</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>373226</t>
+          <t>372187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400991</t>
+          <t>401206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405160</t>
+          <t>406649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459343</t>
+          <t>459869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>790443</t>
+          <t>790903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>848834</t>
+          <t>845815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74180</t>
+          <t>73063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110805</t>
+          <t>110766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87525</t>
+          <t>85998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135247</t>
+          <t>136778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176403</t>
+          <t>179564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234033</t>
+          <t>236256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>425533</t>
+          <t>425572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462158</t>
+          <t>463275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456755</t>
+          <t>455224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>504477</t>
+          <t>506004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>894307</t>
+          <t>892084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>951937</t>
+          <t>948776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>30089</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99658</t>
+          <t>100202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72185</t>
+          <t>72684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104372</t>
+          <t>104156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>95666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193459</t>
+          <t>193469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>788128</t>
+          <t>787584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>859594</t>
+          <t>857697</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608509</t>
+          <t>608725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640696</t>
+          <t>640197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1407208</t>
+          <t>1407198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1506862</t>
+          <t>1505001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22339</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>42611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34524</t>
+          <t>34110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53939</t>
+          <t>52812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61335</t>
+          <t>62750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89661</t>
+          <t>90189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>518437</t>
+          <t>518623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538796</t>
+          <t>538895</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>493966</t>
+          <t>495093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513381</t>
+          <t>513795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1019478</t>
+          <t>1018950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1047804</t>
+          <t>1046389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>21136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>450536</t>
+          <t>432411</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>576650</t>
+          <t>581674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>347901</t>
+          <t>347029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>359245</t>
+          <t>359262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157832</t>
+          <t>175957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>571450</t>
+          <t>571768</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>399883</t>
+          <t>394859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>928211</t>
+          <t>928277</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>26838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39489</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40335</t>
+          <t>40491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60824</t>
+          <t>60187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255019</t>
+          <t>255921</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>269355</t>
+          <t>269479</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386342</t>
+          <t>386669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>401737</t>
+          <t>401413</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>647766</t>
+          <t>648403</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>668255</t>
+          <t>668099</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>211217</t>
+          <t>209116</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>305947</t>
+          <t>305479</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>423866</t>
+          <t>422326</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1213729</t>
+          <t>1190097</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>678344</t>
+          <t>678095</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1552438</t>
+          <t>1452481</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3153870</t>
+          <t>3154338</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3248600</t>
+          <t>3250701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2498551</t>
+          <t>2522183</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3288414</t>
+          <t>3289954</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5619659</t>
+          <t>5719616</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6493753</t>
+          <t>6494002</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51353</t>
+          <t>51497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75911</t>
+          <t>76458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85148</t>
+          <t>85807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119041</t>
+          <t>117762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141366</t>
+          <t>141226</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163222</t>
+          <t>164262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113862</t>
+          <t>113315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138420</t>
+          <t>138276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262559</t>
+          <t>263838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>296452</t>
+          <t>295793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161204</t>
+          <t>161037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195826</t>
+          <t>196324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>295235</t>
+          <t>293512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328963</t>
+          <t>328191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>465538</t>
+          <t>464155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>517280</t>
+          <t>514357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111637</t>
+          <t>111139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146259</t>
+          <t>146426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78769</t>
+          <t>79541</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112497</t>
+          <t>114220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197915</t>
+          <t>200838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249657</t>
+          <t>251040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>284426</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>331836</t>
+          <t>328933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>385074</t>
+          <t>384875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>431566</t>
+          <t>429948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>680254</t>
+          <t>685313</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>744192</t>
+          <t>746858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178493</t>
+          <t>181396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225903</t>
+          <t>224838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157926</t>
+          <t>159544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204418</t>
+          <t>204617</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355630</t>
+          <t>352964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>419568</t>
+          <t>414509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>103204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135830</t>
+          <t>137557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112647</t>
+          <t>112577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143742</t>
+          <t>143904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220787</t>
+          <t>223638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270292</t>
+          <t>270049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154208</t>
+          <t>152481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189309</t>
+          <t>186834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94301</t>
+          <t>94139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125396</t>
+          <t>125466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257790</t>
+          <t>258033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307295</t>
+          <t>304444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30771</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57515</t>
+          <t>56667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83800</t>
+          <t>83519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77213</t>
+          <t>78492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108502</t>
+          <t>110936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77331</t>
+          <t>76693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93573</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116579</t>
+          <t>116860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142864</t>
+          <t>143712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>199979</t>
+          <t>197545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231268</t>
+          <t>229989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27123</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36599</t>
+          <t>36727</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>60359</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52795</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80820</t>
+          <t>80230</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265460</t>
+          <t>265583</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281352</t>
+          <t>281476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280499</t>
+          <t>281676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305436</t>
+          <t>305308</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>553798</t>
+          <t>554388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>581823</t>
+          <t>584211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40793</t>
+          <t>41544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38215</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67028</t>
+          <t>65083</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178673</t>
+          <t>179062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195181</t>
+          <t>195716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>293115</t>
+          <t>292364</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>314639</t>
+          <t>314792</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>476763</t>
+          <t>478708</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>505576</t>
+          <t>505414</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>666019</t>
+          <t>664139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>749273</t>
+          <t>750667</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1015276</t>
+          <t>1014719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1109391</t>
+          <t>1108578</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1698777</t>
+          <t>1695103</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1830993</t>
+          <t>1826314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1160953</t>
+          <t>1159559</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1244207</t>
+          <t>1246087</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1191971</t>
+          <t>1192784</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1286086</t>
+          <t>1286643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2380595</t>
+          <t>2385274</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2512811</t>
+          <t>2516485</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>41941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68910</t>
+          <t>66596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104739</t>
+          <t>104625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132882</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152626</t>
+          <t>152421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190474</t>
+          <t>190678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107570</t>
+          <t>109884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134732</t>
+          <t>134539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83908</t>
+          <t>84338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112051</t>
+          <t>112165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>202795</t>
+          <t>202591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240643</t>
+          <t>240848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,24%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200213</t>
+          <t>199797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234041</t>
+          <t>235210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>378269</t>
+          <t>378744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>401701</t>
+          <t>401940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>588534</t>
+          <t>588341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>629190</t>
+          <t>631642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86491</t>
+          <t>85322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120319</t>
+          <t>120735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46527</t>
+          <t>46052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116138</t>
+          <t>113686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156794</t>
+          <t>156987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>404524</t>
+          <t>399593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>445557</t>
+          <t>444548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>567435</t>
+          <t>565359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>588955</t>
+          <t>587928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>975867</t>
+          <t>977266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1027941</t>
+          <t>1026595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123998</t>
+          <t>125007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165031</t>
+          <t>169962</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20810</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42330</t>
+          <t>44406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151380</t>
+          <t>152726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203454</t>
+          <t>202055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222162</t>
+          <t>224328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262739</t>
+          <t>261854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252400</t>
+          <t>250279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277849</t>
+          <t>276984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>483468</t>
+          <t>483611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>531302</t>
+          <t>531882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112435</t>
+          <t>113320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153012</t>
+          <t>150846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>30732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>57437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151588</t>
+          <t>151008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>199422</t>
+          <t>199279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52673</t>
+          <t>52169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76972</t>
+          <t>76816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>86559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115201</t>
+          <t>117307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146240</t>
+          <t>145617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185228</t>
+          <t>186677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64792</t>
+          <t>64948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89091</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106917</t>
+          <t>104811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137639</t>
+          <t>135559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178654</t>
+          <t>177205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217642</t>
+          <t>218265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23219</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>45118</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64565</t>
+          <t>64275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64705</t>
+          <t>64818</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100299</t>
+          <t>98154</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258864</t>
+          <t>260869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282768</t>
+          <t>284015</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>285345</t>
+          <t>285635</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311688</t>
+          <t>312896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>555598</t>
+          <t>557743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>591192</t>
+          <t>591079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>31932</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>33676</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61029</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51667</t>
+          <t>49769</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83441</t>
+          <t>84560</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>215429</t>
+          <t>215903</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236065</t>
+          <t>236419</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>324706</t>
+          <t>325821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352185</t>
+          <t>352059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>550129</t>
+          <t>549010</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>581903</t>
+          <t>583801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1006836</t>
+          <t>1010607</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1105466</t>
+          <t>1101968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1497883</t>
+          <t>1501790</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1594913</t>
+          <t>1599144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2525671</t>
+          <t>2535549</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2665308</t>
+          <t>2675987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1031860</t>
+          <t>1035358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1130490</t>
+          <t>1126719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>921917</t>
+          <t>917686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1018947</t>
+          <t>1015040</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1988848</t>
+          <t>1978169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2128485</t>
+          <t>2118607</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37397</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62296</t>
+          <t>61312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89734</t>
+          <t>88298</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114120</t>
+          <t>114915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>133347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170094</t>
+          <t>168907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92433</t>
+          <t>93417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117332</t>
+          <t>116977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60829</t>
+          <t>60034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85215</t>
+          <t>86651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159584</t>
+          <t>160771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197012</t>
+          <t>196331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178295</t>
+          <t>179523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208258</t>
+          <t>207657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>299095</t>
+          <t>297647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>322802</t>
+          <t>322360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>484373</t>
+          <t>484394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>522791</t>
+          <t>524199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52439</t>
+          <t>53040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82402</t>
+          <t>81174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>60746</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96299</t>
+          <t>94891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134717</t>
+          <t>134696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>314358</t>
+          <t>312942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>352789</t>
+          <t>352571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>413290</t>
+          <t>412143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>449489</t>
+          <t>448948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>737890</t>
+          <t>737510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>792094</t>
+          <t>790986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111587</t>
+          <t>111805</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150018</t>
+          <t>151434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91720</t>
+          <t>92261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127919</t>
+          <t>129066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213490</t>
+          <t>214598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267694</t>
+          <t>268074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154830</t>
+          <t>155138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193381</t>
+          <t>193472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177841</t>
+          <t>177602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213682</t>
+          <t>211793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>341216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>396733</t>
+          <t>393930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146577</t>
+          <t>146486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185128</t>
+          <t>184820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102174</t>
+          <t>104063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138015</t>
+          <t>138254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259081</t>
+          <t>261884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312675</t>
+          <t>314598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54229</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47447</t>
+          <t>49168</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76060</t>
+          <t>75811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86702</t>
+          <t>86002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122389</t>
+          <t>122675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76005</t>
+          <t>76948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98052</t>
+          <t>98469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128521</t>
+          <t>128770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157134</t>
+          <t>155413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212426</t>
+          <t>212140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>248113</t>
+          <t>248813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>35182</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34027</t>
+          <t>32797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58882</t>
+          <t>60757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54505</t>
+          <t>56321</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87044</t>
+          <t>88272</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264290</t>
+          <t>265446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284795</t>
+          <t>284782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>287317</t>
+          <t>285442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312172</t>
+          <t>313402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559783</t>
+          <t>558555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>592322</t>
+          <t>590506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38058</t>
+          <t>37692</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67715</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54011</t>
+          <t>54555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88944</t>
+          <t>88736</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>219388</t>
+          <t>219003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234421</t>
+          <t>234217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326118</t>
+          <t>325080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355775</t>
+          <t>356141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>551196</t>
+          <t>551404</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>586129</t>
+          <t>585585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>797796</t>
+          <t>800754</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>881605</t>
+          <t>881590</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1146440</t>
+          <t>1148280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1247762</t>
+          <t>1246540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1960395</t>
+          <t>1974561</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2097694</t>
+          <t>2109294</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1015323</t>
+          <t>1015338</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1099132</t>
+          <t>1096174</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1087258</t>
+          <t>1088480</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1188580</t>
+          <t>1186740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2134254</t>
+          <t>2122654</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2271553</t>
+          <t>2257387</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>27815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>43470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>27251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50222</t>
+          <t>60283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>388392</t>
+          <t>394141</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376050</t>
+          <t>379978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395979</t>
+          <t>401385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>292460</t>
+          <t>335177</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279793</t>
+          <t>319042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302089</t>
+          <t>347065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>680852</t>
+          <t>729318</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>662965</t>
+          <t>710022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>692242</t>
+          <t>743054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33674</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>63375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84638</t>
+          <t>99698</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>83333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>118210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>118312</t>
+          <t>145370</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89825</t>
+          <t>122014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144737</t>
+          <t>174334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>389873</t>
+          <t>431218</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372187</t>
+          <t>413515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401206</t>
+          <t>445972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>427455</t>
+          <t>402035</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>406649</t>
+          <t>383523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459869</t>
+          <t>418400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>817328</t>
+          <t>833253</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>790903</t>
+          <t>804289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>845815</t>
+          <t>856609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90853</t>
+          <t>106312</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>86307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110766</t>
+          <t>126719</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>117549</t>
+          <t>137889</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85998</t>
+          <t>119845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136778</t>
+          <t>155075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>208402</t>
+          <t>244201</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179564</t>
+          <t>218856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236256</t>
+          <t>274462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>445485</t>
+          <t>514525</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>425572</t>
+          <t>494118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463275</t>
+          <t>534530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>474453</t>
+          <t>485304</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455224</t>
+          <t>468118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>506004</t>
+          <t>503348</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>919938</t>
+          <t>999828</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>892084</t>
+          <t>969567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>948776</t>
+          <t>1025173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66636</t>
+          <t>75830</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>60458</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100202</t>
+          <t>94195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88449</t>
+          <t>101470</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72684</t>
+          <t>86846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104156</t>
+          <t>117284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>155085</t>
+          <t>177300</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>156936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193469</t>
+          <t>200516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>821150</t>
+          <t>624787</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>787584</t>
+          <t>606422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>857697</t>
+          <t>640159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>624432</t>
+          <t>635416</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608725</t>
+          <t>619602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640197</t>
+          <t>650040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1445582</t>
+          <t>1260204</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1407198</t>
+          <t>1236988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1505001</t>
+          <t>1280568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31387</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22339</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42611</t>
+          <t>46903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42978</t>
+          <t>50104</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34110</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52812</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>84897</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>70021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90189</t>
+          <t>101761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>529847</t>
+          <t>574553</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>518623</t>
+          <t>562443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538895</t>
+          <t>584417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>504927</t>
+          <t>558751</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>495093</t>
+          <t>547615</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513795</t>
+          <t>569031</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1034774</t>
+          <t>1133305</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1018950</t>
+          <t>1116441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1046389</t>
+          <t>1148181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>232082</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>432411</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>246135</t>
+          <t>47067</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48256</t>
+          <t>37947</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>581674</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>354112</t>
+          <t>391108</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>347029</t>
+          <t>383412</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>359262</t>
+          <t>396461</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>376286</t>
+          <t>408071</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175957</t>
+          <t>399101</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>571768</t>
+          <t>414810</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>730398</t>
+          <t>799179</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>394859</t>
+          <t>787603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>928277</t>
+          <t>808299</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26838</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30738</t>
+          <t>33048</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39162</t>
+          <t>42407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>50055</t>
+          <t>54055</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40491</t>
+          <t>43748</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>66056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>263442</t>
+          <t>289191</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255921</t>
+          <t>281109</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>269479</t>
+          <t>295187</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>395093</t>
+          <t>431561</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386669</t>
+          <t>422202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>401413</t>
+          <t>439140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>658535</t>
+          <t>720752</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>648403</t>
+          <t>708751</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>668099</t>
+          <t>731059</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>267516</t>
+          <t>313239</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>209116</t>
+          <t>280385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>305479</t>
+          <t>350896</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>617174</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>422326</t>
+          <t>439680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1190097</t>
+          <t>517265</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>884690</t>
+          <t>793878</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>678095</t>
+          <t>743311</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1452481</t>
+          <t>849666</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3192301</t>
+          <t>3219523</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3154338</t>
+          <t>3181866</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3250701</t>
+          <t>3252377</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3095106</t>
+          <t>3256316</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2522183</t>
+          <t>3219689</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3289954</t>
+          <t>3297274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6287407</t>
+          <t>6475838</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5719616</t>
+          <t>6420050</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6494002</t>
+          <t>6526405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
